--- a/Analyse_et_Conception/Matrice_Role_Permissions.xlsx
+++ b/Analyse_et_Conception/Matrice_Role_Permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmaisonneuveqcca-my.sharepoint.com/personal/e2486153_cmaisonneuve_qc_ca/Documents/Cours/2025-2026/2026_Session_Hiver/Projet_2/Analyse_et_Conception/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_AD4D9D64A577C15A4A54183BC098562A5BDEDD8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FFA94DB-4B9D-4C0E-9733-FB4E3E5D3B02}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="11_AD4D9D64A577C15A4A54183BC098562A5BDEDD8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46123267-9887-4BFF-8BFA-F52503FF9453}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Role_Permissions" sheetId="2" r:id="rId1"/>
@@ -25,45 +25,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Roles \ Permissions</t>
-  </si>
-  <si>
-    <t>Admins</t>
-  </si>
-  <si>
-    <t>Utilisateurs</t>
-  </si>
-  <si>
-    <t>Clients</t>
-  </si>
-  <si>
-    <t>Voir les demandes des Clients</t>
-  </si>
-  <si>
-    <t>Créer une demande</t>
-  </si>
-  <si>
-    <t>Aucun</t>
-  </si>
-  <si>
-    <t>Créer un Client</t>
-  </si>
-  <si>
-    <t>Créer un Utilisateur</t>
-  </si>
-  <si>
-    <t>Ajouter/modifer des permissions</t>
-  </si>
-  <si>
-    <t>Finir demande Clients</t>
-  </si>
-  <si>
-    <t>Supprimer un client</t>
-  </si>
-  <si>
-    <t>Supprimer un utilisateur</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Se connecter à un compte</t>
+  </si>
+  <si>
+    <t>Créer un compte Client</t>
+  </si>
+  <si>
+    <t>Permissions /Roles</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Utilisateur (Employe)</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Non connecté / Aucune Role</t>
+  </si>
+  <si>
+    <t>Gérer les Utilisateurs
+- Modifier 
+- Ajouter
+- Supprimer
+- Attribution des rôles
+-Lister les Utilisateurs</t>
+  </si>
+  <si>
+    <t>Faire une demande d'immigration</t>
+  </si>
+  <si>
+    <t>Fermer un dossier d'un client</t>
+  </si>
+  <si>
+    <t>Gérer les Clients
+- Modifier 
+- Ajouter
+- Supprimer
+- Attribution des rôles
+-Lister les clients
+- Voir leur dossier
+- Répondre au demandes
+- Modifier leur état (résidents temporaires, permanents, etc)</t>
   </si>
 </sst>
 </file>
@@ -105,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -114,39 +121,14 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
@@ -189,19 +171,19 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}" name="Role_Permissions" displayName="Role_Permissions" ref="A1:I5" totalsRowShown="0">
-  <autoFilter ref="A1:I5" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{D246AD2C-A076-449E-81C6-EB3800922C21}" name="Roles \ Permissions"/>
-    <tableColumn id="2" xr3:uid="{1D1E9A75-CBDE-4D00-882B-6F42215CF277}" name="Voir les demandes des Clients"/>
-    <tableColumn id="3" xr3:uid="{6AD3132D-A5EC-4767-9F06-2FEFD369D1A6}" name="Créer une demande"/>
-    <tableColumn id="4" xr3:uid="{AD61A48C-4395-405D-A530-C54588A8D1DF}" name="Créer un Client"/>
-    <tableColumn id="5" xr3:uid="{136479DD-2956-47C4-8FDD-821A29B328B9}" name="Créer un Utilisateur" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{BFF47D4F-AC6E-4A11-B062-BB0A5F9891D5}" name="Ajouter/modifer des permissions" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{138D8A71-0E59-47C7-8F49-0F595E29DC40}" name="Finir demande Clients" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{82407B16-0B60-4BEE-8EC7-D768D6E78594}" name="Supprimer un client" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{E1BB8F74-1C4F-4329-98F7-DBE195E0FA49}" name="Supprimer un utilisateur" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}" name="Role_Permissions" displayName="Role_Permissions" ref="A1:E7" totalsRowShown="0">
+  <autoFilter ref="A1:E7" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D246AD2C-A076-449E-81C6-EB3800922C21}" name="Permissions /Roles"/>
+    <tableColumn id="2" xr3:uid="{1D1E9A75-CBDE-4D00-882B-6F42215CF277}" name="Admin"/>
+    <tableColumn id="3" xr3:uid="{6AD3132D-A5EC-4767-9F06-2FEFD369D1A6}" name="Utilisateur (Employe)"/>
+    <tableColumn id="4" xr3:uid="{AD61A48C-4395-405D-A530-C54588A8D1DF}" name="Client"/>
+    <tableColumn id="5" xr3:uid="{136479DD-2956-47C4-8FDD-821A29B328B9}" name="Non connecté / Aucune Role" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -470,162 +452,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB7CCC7-C502-468F-9A78-FCB622B9B671}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="b">
+      <c r="B7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Analyse_et_Conception/Matrice_Role_Permissions.xlsx
+++ b/Analyse_et_Conception/Matrice_Role_Permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmaisonneuveqcca-my.sharepoint.com/personal/e2486153_cmaisonneuve_qc_ca/Documents/Cours/2025-2026/2026_Session_Hiver/Projet_2/Analyse_et_Conception/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="11_AD4D9D64A577C15A4A54183BC098562A5BDEDD8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46123267-9887-4BFF-8BFA-F52503FF9453}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="11_AD4D9D64A577C15A4A54183BC098562A5BDEDD8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{885CD97B-BCA2-4146-B234-FDFDB545D3F3}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Se connecter à un compte</t>
   </si>
@@ -62,15 +62,22 @@
     <t>Fermer un dossier d'un client</t>
   </si>
   <si>
+    <t>Ajouter/Supprimer des documents dans un dossier</t>
+  </si>
+  <si>
+    <t>//L'admin peut acceder à toute les permissions de tous les autres roles dans la sid- bar</t>
+  </si>
+  <si>
     <t>Gérer les Clients
 - Modifier 
 - Ajouter
 - Supprimer
 - Attribution des rôles
 -Lister les clients
-- Voir leur dossier
+- Voir les dossier des clients
 - Répondre au demandes
-- Modifier leur état (résidents temporaires, permanents, etc)</t>
+- Modifier leur état (résidents temporaires, permanents, etc)
+- Voir les factures</t>
   </si>
 </sst>
 </file>
@@ -176,8 +183,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}" name="Role_Permissions" displayName="Role_Permissions" ref="A1:E7" totalsRowShown="0">
-  <autoFilter ref="A1:E7" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}" name="Role_Permissions" displayName="Role_Permissions" ref="A1:E8" totalsRowShown="0">
+  <autoFilter ref="A1:E8" xr:uid="{0E630B8F-A185-4521-8D31-44491E88D3E0}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D246AD2C-A076-449E-81C6-EB3800922C21}" name="Permissions /Roles"/>
     <tableColumn id="2" xr3:uid="{1D1E9A75-CBDE-4D00-882B-6F42215CF277}" name="Admin"/>
@@ -452,21 +459,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB7CCC7-C502-468F-9A78-FCB622B9B671}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
     <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -483,7 +490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -500,7 +507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -517,9 +524,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="b">
         <v>1</v>
@@ -534,7 +541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -551,12 +558,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="b">
         <v>0</v>
@@ -567,8 +574,11 @@
       <c r="E6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -582,6 +592,23 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="b">
         <v>0</v>
       </c>
     </row>
